--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6035" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="788">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}empfindlichkeit-kategorie-braucht-interpretation:If the result is given as a susceptibility category rather than a measured value, Observation.interpretation SHALL be present, because the norm it was derived from is carried there. {value.ofType(CodeableConcept).exists() implies interpretation.exists()}empfindlichkeit-kategorie-stimmt-mit-interpretation:Where both a categorical result value and an interpretation are given, every code of the value SHALL also appear among the interpretation codes. {value.ofType(CodeableConcept).coding.code.subsetOf(interpretation.coding.code)}empfindlichkeit-messwert-sollte-bewertet-sein:Where the result is a measured value, an interpretation SHOULD be given. It may be absent where no breakpoints are defined for the organism and agent. {value.ofType(Quantity).exists() implies interpretation.exists()}</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -1349,7 +1349,7 @@
 </t>
   </si>
   <si>
-    <t>Es werden bevorzugt LOINC-Codes ohne präkoordinierte Specimentype-Angabe verwendet (System = XXX); der Specimentype wird separat über Specimen.type kodiert.</t>
+    <t>Bevorzugt LOINC-Codes OHNE praekoordiniertes Verfahren, z. B. 100044-7 'Cefcapene [Susceptibility]' und nicht die '... by Broth dilution'-Variante — das Verfahren gehoert nach Observation.method. Das EU-Datenmodell markiert diese methodenfreie Menge als 'methodless:true' und Preferred. Ebenso bevorzugt ohne praekoordinierte Specimentype-Angabe (System = XXX); der Specimentype wird separat ueber Specimen.type kodiert. NICHT hierher gehoeren Codes mit der Methode 'Genotyping', etwa 103958-5 'Ofloxacin [Susceptibility] by Genotype': Dieses Profil verlangt ein Grenzwert-Regelwerk in interpretation.extension[Norm], und eine genotypische Vorhersage beruht auf keinem. Sie gehoert nach MII_PR_Mikrobio_Voraussichtliche_Empfindlichkeit.</t>
   </si>
   <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
@@ -1659,39 +1659,43 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
+    <t>Quantity
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Messwert</t>
+  </si>
+  <si>
+    <t>Wert der Analyse</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>ele-1
+obs-7</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
-    <t>Messwert</t>
-  </si>
-  <si>
-    <t>Wert der Analyse</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-7</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
     <t>Actual result</t>
   </si>
   <si>
@@ -1901,7 +1905,10 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-codiert</t>
+    <t>Die Empfindlichkeitskategorie, wenn kein Messwert vorliegt. Aus derselben Liste wie interpretation, weil beide dasselbe aussagen — sind beide angegeben, muessen sie uebereinstimmen (empfindlichkeit-kategorie-stimmt-mit-interpretation).</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-susceptibility</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -2026,9 +2033,6 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-susceptibility</t>
-  </si>
-  <si>
     <t>Observation.interpretation.id</t>
   </si>
   <si>
@@ -2104,10 +2108,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-empfindlichkeit-methode-snomed</t>
   </si>
   <si>
     <t>Observation.method.id</t>
@@ -2146,7 +2147,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -2836,7 +2837,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="140.3671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.91796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="98.4609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -13414,13 +13415,13 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>524</v>
@@ -13492,10 +13493,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13592,10 +13593,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13694,13 +13695,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="B107" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="C107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>104</v>
@@ -13722,16 +13723,16 @@
         <v>77</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13798,10 +13799,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13824,19 +13825,19 @@
         <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13885,7 +13886,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -13902,10 +13903,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14002,10 +14003,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14104,13 +14105,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>104</v>
@@ -14132,16 +14133,16 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14208,10 +14209,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14234,13 +14235,13 @@
         <v>77</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14291,7 +14292,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
@@ -14308,10 +14309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14337,22 +14338,22 @@
         <v>160</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>77</v>
@@ -14376,10 +14377,10 @@
         <v>226</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>77</v>
@@ -14397,7 +14398,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14414,10 +14415,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14443,16 +14444,16 @@
         <v>99</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -14501,7 +14502,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
@@ -14518,10 +14519,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14547,23 +14548,23 @@
         <v>126</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -14605,7 +14606,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -14614,7 +14615,7 @@
         <v>84</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>92</v>
@@ -14622,10 +14623,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14651,16 +14652,16 @@
         <v>160</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14689,7 +14690,7 @@
       </c>
       <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>77</v>
@@ -14707,7 +14708,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14724,13 +14725,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>520</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>77</v>
@@ -14755,10 +14756,10 @@
         <v>283</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>531</v>
+        <v>600</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>524</v>
@@ -14793,7 +14794,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>77</v>
@@ -14828,10 +14829,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14928,10 +14929,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15030,10 +15031,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15134,10 +15135,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15234,10 +15235,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15336,10 +15337,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15440,10 +15441,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15542,10 +15543,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15646,10 +15647,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15750,10 +15751,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15854,10 +15855,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15958,13 +15959,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>520</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>77</v>
@@ -15986,13 +15987,13 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>524</v>
@@ -16064,13 +16065,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>520</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
@@ -16092,13 +16093,13 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>524</v>
@@ -16170,10 +16171,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16199,16 +16200,16 @@
         <v>283</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16237,7 +16238,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -16255,7 +16256,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -16264,7 +16265,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>92</v>
@@ -16272,14 +16273,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16301,16 +16302,16 @@
         <v>283</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16339,7 +16340,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -16357,7 +16358,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16374,10 +16375,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16474,10 +16475,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16574,13 +16575,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="B135" t="s" s="2">
-        <v>641</v>
-      </c>
       <c r="C135" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>77</v>
@@ -16602,7 +16603,7 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>196</v>
@@ -16676,10 +16677,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16780,10 +16781,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16884,10 +16885,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16910,19 +16911,19 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -16971,7 +16972,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
@@ -16988,10 +16989,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17017,13 +17018,13 @@
         <v>283</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17052,10 +17053,10 @@
         <v>150</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -17073,7 +17074,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>75</v>
@@ -17090,10 +17091,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17119,16 +17120,16 @@
         <v>283</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -17153,11 +17154,9 @@
         <v>77</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
         <v>665</v>
       </c>
@@ -17177,7 +17176,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
@@ -20596,7 +20595,7 @@
         <v>77</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L174" t="s" s="2">
         <v>738</v>
@@ -21526,7 +21525,7 @@
         <v>772</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>773</v>
@@ -21636,7 +21635,7 @@
         <v>777</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
@@ -21694,7 +21693,7 @@
         <v>84</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>92</v>
@@ -21709,7 +21708,7 @@
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
@@ -21737,10 +21736,10 @@
         <v>782</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$187</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6065" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Dieses Profil beschreibt die phänotypische Empfindlichkeitstestung. Die Resistenz eines bereits identifizierten Erregers gegen eine einzelne Substanz wird hier abgebildet, z. B. ein linezolidresistenter Enterococcus über 29258-1 |Linezolid [Susceptibility]| mit interpretation R; der Negativfall ist interpretation S. Der zielgerichtete Nachweis eines resistenten Erregers als solchen gehört dagegen nach MII_PR_Mikrobio_Spezifische_Bestimmung bzw. MII_PR_Mikrobio_Spezifische_Kultur.</t>
+    <t>Dieses Profil beschreibt die phänotypische Empfindlichkeitstestung. Die Resistenz eines bereits identifizierten Erregers gegen eine einzelne Substanz wird hier abgebildet, z. B. ein linezolidresistenter Enterococcus über 29258-1 |Linezolid [Susceptibility]| mit interpretation R; der Negativfall ist interpretation S. Der zielgerichtete Nachweis eines resistenten Erregers als solchen gehört dagegen nach MII_PR_Mikrobio_Spezifische_Bestimmung.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}empfindlichkeit-kategorie-braucht-interpretation:If the result is given as a susceptibility category rather than a measured value, Observation.interpretation SHALL be present, because the norm it was derived from is carried there. {value.ofType(CodeableConcept).exists() implies interpretation.exists()}empfindlichkeit-kategorie-stimmt-mit-interpretation:Where both a categorical result value and an interpretation are given, every code of the value SHALL also appear among the interpretation codes. {value.ofType(CodeableConcept).coding.code.subsetOf(interpretation.coding.code)}empfindlichkeit-messwert-sollte-bewertet-sein:Where the result is a measured value, an interpretation SHOULD be given. It may be absent where no breakpoints are defined for the organism and agent. {value.ofType(Quantity).exists() implies interpretation.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}empfindlichkeit-messwert-sollte-bewertet-sein:Where the result is a measured value, an interpretation SHOULD be given. It may be absent where no breakpoints are defined for the organism and agent. {value.ofType(Quantity).exists() implies interpretation.exists()}</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -1905,7 +1905,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Die Empfindlichkeitskategorie, wenn kein Messwert vorliegt. Aus derselben Liste wie interpretation, weil beide dasselbe aussagen — sind beide angegeben, muessen sie uebereinstimmen (empfindlichkeit-kategorie-stimmt-mit-interpretation).</t>
+    <t>Die Empfindlichkeitskategorie, wenn kein Messwert vorliegt. Aus derselben Liste wie interpretation, weil beide dasselbe aussagen; sind beide angegeben, muessen sie dieselbe Kategorie nennen. Die Norm steht dann an derjenigen Stelle, an der die Kategorie steht — hier in valueCodeableConcept.extension[Norm].</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-susceptibility</t>
@@ -1915,6 +1915,16 @@
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.extension:Norm</t>
+  </si>
+  <si>
+    <t>Norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-ex-mikrobio-empfindlichkeit-norm}
+</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.coding</t>
@@ -2040,13 +2050,6 @@
   </si>
   <si>
     <t>Observation.interpretation.extension:Norm</t>
-  </si>
-  <si>
-    <t>Norm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-ex-mikrobio-empfindlichkeit-norm}
-</t>
   </si>
   <si>
     <t>Observation.interpretation.coding</t>
@@ -2809,7 +2812,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ186"/>
+  <dimension ref="A1:AJ187"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -14936,11 +14939,11 @@
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>76</v>
@@ -14958,14 +14961,12 @@
         <v>105</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15034,9 +15035,11 @@
         <v>604</v>
       </c>
       <c r="B120" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C120" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>77</v>
       </c>
@@ -15045,7 +15048,7 @@
         <v>84</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>85</v>
@@ -15054,23 +15057,19 @@
         <v>77</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>138</v>
+        <v>606</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>77</v>
       </c>
@@ -15118,7 +15117,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -15130,15 +15129,15 @@
         <v>91</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15146,31 +15145,35 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>77</v>
       </c>
@@ -15218,38 +15221,38 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>102</v>
+        <v>303</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>77</v>
@@ -15261,17 +15264,15 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -15308,75 +15309,73 @@
         <v>77</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>312</v>
+        <v>106</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>77</v>
       </c>
@@ -15412,39 +15411,39 @@
         <v>77</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>317</v>
+        <v>112</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15452,7 +15451,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>84</v>
@@ -15467,18 +15466,20 @@
         <v>85</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
       </c>
@@ -15526,7 +15527,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -15543,10 +15544,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15554,7 +15555,7 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>84</v>
@@ -15569,20 +15570,18 @@
         <v>85</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
@@ -15630,7 +15629,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -15645,12 +15644,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15658,13 +15657,13 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>77</v>
@@ -15673,19 +15672,19 @@
         <v>85</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -15734,7 +15733,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -15751,10 +15750,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15777,19 +15776,19 @@
         <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -15838,7 +15837,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
@@ -15855,10 +15854,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15881,19 +15880,19 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -15942,7 +15941,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15957,16 +15956,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>77</v>
       </c>
@@ -15978,7 +15975,7 @@
         <v>84</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>77</v>
@@ -15987,19 +15984,19 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>624</v>
+        <v>99</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>532</v>
+        <v>348</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>524</v>
+        <v>350</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>525</v>
+        <v>351</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16048,7 +16045,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>520</v>
+        <v>352</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -16057,7 +16054,7 @@
         <v>84</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>528</v>
+        <v>91</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>92</v>
@@ -16174,9 +16171,11 @@
         <v>628</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C131" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="D131" t="s" s="2">
         <v>77</v>
       </c>
@@ -16194,22 +16193,22 @@
         <v>77</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>283</v>
+        <v>630</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>629</v>
+        <v>532</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>630</v>
+        <v>533</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>631</v>
+        <v>524</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>632</v>
+        <v>525</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16234,11 +16233,13 @@
         <v>77</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>633</v>
+        <v>77</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -16256,7 +16257,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>628</v>
+        <v>520</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -16265,7 +16266,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>634</v>
+        <v>528</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>92</v>
@@ -16273,21 +16274,21 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>636</v>
+        <v>77</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>85</v>
@@ -16302,16 +16303,16 @@
         <v>283</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16340,7 +16341,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>601</v>
+        <v>636</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -16358,41 +16359,41 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>91</v>
+        <v>637</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>77</v>
+        <v>639</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>77</v>
@@ -16401,16 +16402,20 @@
         <v>77</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>99</v>
+        <v>283</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>100</v>
+        <v>640</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>641</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
       </c>
@@ -16434,13 +16439,11 @@
         <v>77</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>77</v>
+        <v>601</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -16458,27 +16461,27 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>102</v>
+        <v>638</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16486,10 +16489,10 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>77</v>
@@ -16501,13 +16504,13 @@
         <v>77</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -16546,43 +16549,41 @@
         <v>77</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>77</v>
       </c>
@@ -16591,10 +16592,10 @@
         <v>84</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>77</v>
@@ -16603,7 +16604,7 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>645</v>
+        <v>105</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>196</v>
@@ -16648,16 +16649,16 @@
         <v>77</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF135" t="s" s="2">
         <v>112</v>
@@ -16675,48 +16676,46 @@
         <v>113</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>646</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C136" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="D136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>138</v>
+        <v>606</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>77</v>
       </c>
@@ -16764,7 +16763,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>75</v>
@@ -16776,7 +16775,7 @@
         <v>77</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="137" hidden="true">
@@ -16795,7 +16794,7 @@
         <v>75</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>77</v>
@@ -16807,19 +16806,19 @@
         <v>85</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>348</v>
+        <v>298</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>77</v>
@@ -16868,13 +16867,13 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>77</v>
@@ -16883,7 +16882,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
         <v>648</v>
       </c>
@@ -16899,31 +16898,31 @@
         <v>75</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J138" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K138" t="s" s="2">
-        <v>649</v>
+        <v>99</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>650</v>
+        <v>348</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>651</v>
+        <v>349</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>652</v>
+        <v>350</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>653</v>
+        <v>351</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -16972,27 +16971,27 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>648</v>
+        <v>352</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17003,10 +17002,10 @@
         <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>77</v>
@@ -17015,18 +17014,20 @@
         <v>77</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>283</v>
+        <v>650</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
       </c>
@@ -17050,13 +17051,13 @@
         <v>77</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>658</v>
+        <v>77</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>659</v>
+        <v>77</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -17074,13 +17075,13 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>91</v>
@@ -17089,12 +17090,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17105,10 +17106,10 @@
         <v>75</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>77</v>
@@ -17120,17 +17121,15 @@
         <v>283</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>664</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>77</v>
       </c>
@@ -17154,11 +17153,13 @@
         <v>77</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>659</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>77</v>
@@ -17176,7 +17177,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
@@ -17191,12 +17192,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17210,7 +17211,7 @@
         <v>84</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>77</v>
@@ -17219,16 +17220,20 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>99</v>
+        <v>283</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>100</v>
+        <v>662</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
       </c>
@@ -17252,13 +17257,11 @@
         <v>77</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>77</v>
+        <v>666</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>77</v>
@@ -17276,7 +17279,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>102</v>
+        <v>661</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>75</v>
@@ -17285,10 +17288,10 @@
         <v>84</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="142" hidden="true">
@@ -17300,14 +17303,14 @@
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>77</v>
@@ -17319,17 +17322,15 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -17366,34 +17367,34 @@
         <v>77</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
         <v>668</v>
       </c>
@@ -17402,7 +17403,7 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -17412,29 +17413,27 @@
         <v>76</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>298</v>
+        <v>106</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>299</v>
+        <v>107</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>77</v>
       </c>
@@ -17470,19 +17469,19 @@
         <v>77</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>75</v>
@@ -17494,10 +17493,10 @@
         <v>91</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
         <v>669</v>
       </c>
@@ -17513,28 +17512,32 @@
         <v>75</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>100</v>
+        <v>298</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
       </c>
@@ -17582,19 +17585,19 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>102</v>
+        <v>303</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="145" hidden="true">
@@ -17606,14 +17609,14 @@
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>77</v>
@@ -17625,17 +17628,15 @@
         <v>77</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -17672,34 +17673,34 @@
         <v>77</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
         <v>671</v>
       </c>
@@ -17708,39 +17709,37 @@
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>312</v>
+        <v>106</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>77</v>
       </c>
@@ -17776,34 +17775,34 @@
         <v>77</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>317</v>
+        <v>112</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>672</v>
       </c>
@@ -17816,13 +17815,13 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>77</v>
@@ -17831,18 +17830,20 @@
         <v>85</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
       </c>
@@ -17890,7 +17891,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -17905,7 +17906,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
         <v>673</v>
       </c>
@@ -17918,13 +17919,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>77</v>
@@ -17933,20 +17934,18 @@
         <v>85</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>77</v>
       </c>
@@ -17994,7 +17993,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -18022,7 +18021,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>84</v>
@@ -18037,19 +18036,19 @@
         <v>85</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -18098,7 +18097,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>75</v>
@@ -18113,7 +18112,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>675</v>
       </c>
@@ -18132,7 +18131,7 @@
         <v>84</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>77</v>
@@ -18141,19 +18140,19 @@
         <v>85</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -18202,7 +18201,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -18245,19 +18244,19 @@
         <v>85</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -18306,7 +18305,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -18321,7 +18320,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
         <v>677</v>
       </c>
@@ -18334,33 +18333,35 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J152" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K152" t="s" s="2">
-        <v>678</v>
+        <v>99</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>679</v>
+        <v>348</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>680</v>
+        <v>349</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O152" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
       </c>
@@ -18408,7 +18409,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>677</v>
+        <v>352</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
@@ -18420,15 +18421,15 @@
         <v>91</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>383</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18436,13 +18437,13 @@
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>77</v>
@@ -18451,15 +18452,17 @@
         <v>77</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>99</v>
+        <v>679</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>100</v>
+        <v>680</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N153" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -18508,7 +18511,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>102</v>
+        <v>678</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
@@ -18517,10 +18520,10 @@
         <v>84</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
     </row>
     <row r="154" hidden="true">
@@ -18532,14 +18535,14 @@
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>77</v>
@@ -18551,17 +18554,15 @@
         <v>77</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -18598,34 +18599,34 @@
         <v>77</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
         <v>684</v>
       </c>
@@ -18634,35 +18635,35 @@
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>453</v>
+        <v>106</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>454</v>
+        <v>107</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>455</v>
+        <v>108</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -18700,34 +18701,34 @@
         <v>77</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>456</v>
+        <v>112</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>457</v>
+        <v>91</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>685</v>
       </c>
@@ -18746,7 +18747,7 @@
         <v>84</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>77</v>
@@ -18755,16 +18756,16 @@
         <v>85</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -18790,13 +18791,13 @@
         <v>77</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>462</v>
+        <v>77</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>77</v>
@@ -18814,7 +18815,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>75</v>
@@ -18823,13 +18824,13 @@
         <v>84</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>91</v>
+        <v>457</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
         <v>686</v>
       </c>
@@ -18848,7 +18849,7 @@
         <v>84</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>77</v>
@@ -18857,16 +18858,16 @@
         <v>85</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18892,13 +18893,13 @@
         <v>77</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>77</v>
@@ -18916,7 +18917,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -18931,7 +18932,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>687</v>
       </c>
@@ -18950,7 +18951,7 @@
         <v>84</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>77</v>
@@ -18959,16 +18960,16 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -19018,7 +19019,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -19033,7 +19034,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
         <v>688</v>
       </c>
@@ -19052,25 +19053,25 @@
         <v>84</v>
       </c>
       <c r="H159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J159" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I159" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K159" t="s" s="2">
-        <v>689</v>
+        <v>99</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>690</v>
+        <v>471</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>691</v>
+        <v>472</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>692</v>
+        <v>473</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -19120,7 +19121,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>688</v>
+        <v>474</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -19132,15 +19133,15 @@
         <v>91</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>383</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19154,7 +19155,7 @@
         <v>84</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>77</v>
@@ -19163,15 +19164,17 @@
         <v>77</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>99</v>
+        <v>690</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>100</v>
+        <v>691</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>693</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -19220,7 +19223,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>102</v>
+        <v>689</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
@@ -19229,10 +19232,10 @@
         <v>84</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
     </row>
     <row r="161" hidden="true">
@@ -19244,14 +19247,14 @@
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>77</v>
@@ -19263,17 +19266,15 @@
         <v>77</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -19310,34 +19311,34 @@
         <v>77</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
         <v>695</v>
       </c>
@@ -19346,35 +19347,35 @@
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>453</v>
+        <v>106</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>454</v>
+        <v>107</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>455</v>
+        <v>108</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -19412,34 +19413,34 @@
         <v>77</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>456</v>
+        <v>112</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>457</v>
+        <v>91</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>696</v>
       </c>
@@ -19458,7 +19459,7 @@
         <v>84</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>77</v>
@@ -19467,16 +19468,16 @@
         <v>85</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -19502,13 +19503,13 @@
         <v>77</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>462</v>
+        <v>77</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>77</v>
@@ -19526,7 +19527,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>75</v>
@@ -19535,13 +19536,13 @@
         <v>84</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>91</v>
+        <v>457</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
         <v>697</v>
       </c>
@@ -19560,7 +19561,7 @@
         <v>84</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>77</v>
@@ -19569,16 +19570,16 @@
         <v>85</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -19604,13 +19605,13 @@
         <v>77</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>77</v>
@@ -19628,7 +19629,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>75</v>
@@ -19643,7 +19644,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>698</v>
       </c>
@@ -19662,7 +19663,7 @@
         <v>84</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>77</v>
@@ -19671,16 +19672,16 @@
         <v>85</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19730,7 +19731,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19745,7 +19746,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
         <v>699</v>
       </c>
@@ -19761,32 +19762,30 @@
         <v>75</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H166" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J166" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I166" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J166" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K166" t="s" s="2">
-        <v>700</v>
+        <v>99</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>701</v>
+        <v>471</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>702</v>
+        <v>472</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>77</v>
       </c>
@@ -19834,27 +19833,27 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>699</v>
+        <v>474</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>705</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19865,10 +19864,10 @@
         <v>75</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>77</v>
@@ -19877,16 +19876,20 @@
         <v>77</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>99</v>
+        <v>701</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>100</v>
+        <v>702</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
       </c>
@@ -19934,19 +19937,19 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>102</v>
+        <v>700</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>77</v>
+        <v>706</v>
       </c>
     </row>
     <row r="168" hidden="true">
@@ -19958,14 +19961,14 @@
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>77</v>
@@ -19977,17 +19980,15 @@
         <v>77</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -20024,31 +20025,31 @@
         <v>77</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="169" hidden="true">
@@ -20060,7 +20061,7 @@
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>709</v>
+        <v>104</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -20073,26 +20074,24 @@
         <v>77</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>710</v>
+        <v>106</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>711</v>
+        <v>107</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="O169" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>77</v>
       </c>
@@ -20128,19 +20127,19 @@
         <v>77</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>712</v>
+        <v>112</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -20155,46 +20154,48 @@
         <v>113</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>77</v>
+        <v>710</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I170" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I170" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J170" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>714</v>
+        <v>105</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O170" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
       </c>
@@ -20248,21 +20249,21 @@
         <v>75</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>718</v>
+        <v>91</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>719</v>
+        <v>113</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20285,16 +20286,16 @@
         <v>77</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20344,27 +20345,27 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="AG171" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>719</v>
-      </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20378,7 +20379,7 @@
         <v>84</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>77</v>
@@ -20387,20 +20388,18 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>283</v>
+        <v>715</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>727</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>77</v>
       </c>
@@ -20424,13 +20423,13 @@
         <v>77</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>728</v>
+        <v>77</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>729</v>
+        <v>77</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>77</v>
@@ -20448,7 +20447,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20457,18 +20456,18 @@
         <v>84</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>91</v>
+        <v>719</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>92</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20479,7 +20478,7 @@
         <v>75</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>77</v>
@@ -20494,16 +20493,16 @@
         <v>283</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -20528,13 +20527,13 @@
         <v>77</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>77</v>
@@ -20552,13 +20551,13 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>91</v>
@@ -20569,10 +20568,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20583,7 +20582,7 @@
         <v>75</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>77</v>
@@ -20595,19 +20594,19 @@
         <v>77</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>624</v>
+        <v>283</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>77</v>
@@ -20632,13 +20631,13 @@
         <v>77</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>77</v>
+        <v>736</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>77</v>
+        <v>737</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>77</v>
@@ -20656,27 +20655,27 @@
         <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>742</v>
+        <v>92</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20699,18 +20698,20 @@
         <v>77</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>99</v>
+        <v>627</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O175" s="2"/>
+        <v>741</v>
+      </c>
+      <c r="O175" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="P175" t="s" s="2">
         <v>77</v>
       </c>
@@ -20758,7 +20759,7 @@
         <v>77</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -20770,15 +20771,15 @@
         <v>91</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>92</v>
+        <v>743</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20789,7 +20790,7 @@
         <v>75</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>77</v>
@@ -20798,19 +20799,19 @@
         <v>77</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>747</v>
+        <v>99</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>750</v>
+        <v>328</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20860,27 +20861,27 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>383</v>
+        <v>92</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20903,16 +20904,16 @@
         <v>85</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -20962,7 +20963,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
@@ -20979,10 +20980,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21005,20 +21006,18 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>700</v>
+        <v>753</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>760</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>77</v>
       </c>
@@ -21066,7 +21065,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>75</v>
@@ -21078,15 +21077,15 @@
         <v>91</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>92</v>
+        <v>383</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21097,7 +21096,7 @@
         <v>75</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>77</v>
@@ -21106,19 +21105,23 @@
         <v>77</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>99</v>
+        <v>701</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>100</v>
+        <v>758</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
+        <v>759</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
       </c>
@@ -21166,19 +21169,19 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>102</v>
+        <v>757</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="180" hidden="true">
@@ -21190,14 +21193,14 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>77</v>
@@ -21209,17 +21212,15 @@
         <v>77</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -21256,31 +21257,31 @@
         <v>77</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row r="181" hidden="true">
@@ -21292,7 +21293,7 @@
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>709</v>
+        <v>104</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -21305,26 +21306,24 @@
         <v>77</v>
       </c>
       <c r="I181" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K181" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>710</v>
+        <v>106</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>711</v>
+        <v>107</v>
       </c>
       <c r="N181" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="O181" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>77</v>
       </c>
@@ -21360,19 +21359,19 @@
         <v>77</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>712</v>
+        <v>112</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -21396,38 +21395,38 @@
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>77</v>
+        <v>710</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I182" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J182" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>767</v>
+        <v>108</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>426</v>
+        <v>251</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>77</v>
@@ -21452,13 +21451,13 @@
         <v>77</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>768</v>
+        <v>77</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>769</v>
+        <v>77</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>77</v>
@@ -21476,27 +21475,27 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>764</v>
+        <v>713</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21504,7 +21503,7 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>84</v>
@@ -21519,19 +21518,19 @@
         <v>85</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>771</v>
+        <v>283</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>533</v>
+        <v>767</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>525</v>
+        <v>426</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>77</v>
@@ -21556,13 +21555,13 @@
         <v>77</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>77</v>
+        <v>769</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>77</v>
+        <v>770</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>77</v>
@@ -21580,10 +21579,10 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>84</v>
@@ -21597,10 +21596,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21620,22 +21619,22 @@
         <v>77</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>283</v>
+        <v>772</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>776</v>
+        <v>533</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>632</v>
+        <v>525</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
@@ -21660,13 +21659,13 @@
         <v>77</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>778</v>
+        <v>77</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>779</v>
+        <v>77</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>77</v>
@@ -21684,7 +21683,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>75</v>
@@ -21693,7 +21692,7 @@
         <v>84</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>634</v>
+        <v>91</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>92</v>
@@ -21701,21 +21700,21 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>636</v>
+        <v>77</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>77</v>
@@ -21730,16 +21729,16 @@
         <v>283</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>639</v>
+        <v>778</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
@@ -21767,10 +21766,10 @@
         <v>142</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>77</v>
@@ -21788,16 +21787,16 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>91</v>
+        <v>637</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>92</v>
@@ -21805,14 +21804,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>77</v>
+        <v>639</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -21831,19 +21830,19 @@
         <v>77</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>703</v>
+        <v>642</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>704</v>
+        <v>643</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -21868,13 +21867,13 @@
         <v>77</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>77</v>
+        <v>784</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>77</v>
+        <v>785</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>77</v>
@@ -21892,7 +21891,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>75</v>
@@ -21901,14 +21900,118 @@
         <v>76</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ186" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ186">
+  <autoFilter ref="A1:AJ187">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21918,7 +22021,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI185">
+  <conditionalFormatting sqref="A2:AI186">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-empfindlichkeit.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
